--- a/outputs/36277.xlsx
+++ b/outputs/36277.xlsx
@@ -499,8 +499,8 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="str">
-        <f aca="false">INDEX($A$1:$E$25,MATCH($I$1,$B$1:$B$25,0),MATCH(H2,$A$1:$E$1,0))</f>
-        <v>Social Media</v>
+        <f aca="false">INDEX($A$1:$E$25, 2, MATCH(H1, $A$1:$E$1, 0))</f>
+        <v>A</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -524,8 +524,8 @@
         <v>2</v>
       </c>
       <c r="I3" s="1" t="str">
-        <f aca="false">INDEX($A$1:$E$25,MATCH($I$1,$B$1:$B$25,0),MATCH(H3,$A$1:$E$1,0))</f>
-        <v>Free</v>
+        <f aca="false">INDEX($A$1:$E$25, 3, MATCH(H1, $A$1:$E$1, 0))</f>
+        <v>B</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -548,9 +548,9 @@
       <c r="H4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <f aca="false">INDEX($A$1:$E$25,MATCH($I$1,$B$1:$B$25,0),MATCH(H4,$A$1:$E$1,0))</f>
-        <v>1500</v>
+      <c r="I4" s="1" t="str">
+        <f aca="false">INDEX($A$1:$E$25, 4, MATCH(H1, $A$1:$E$1, 0))</f>
+        <v>C</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -573,9 +573,9 @@
       <c r="H5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <f aca="false">INDEX($A$1:$E$25,MATCH($I$1,$B$1:$B$25,0),MATCH(H5,$A$1:$E$1,0))</f>
-        <v>1600</v>
+      <c r="I5" s="1" t="str">
+        <f aca="false">INDEX($A$1:$E$25, 5, MATCH(H1, $A$1:$E$1, 0))</f>
+        <v>D</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
